--- a/DB.xlsx
+++ b/DB.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5ac4c140387c5f6/바탕 화면/StudyTime_EveryWhere/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5ac4c140387c5f6/문서/GitHub/Studytime/studytime/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="228" documentId="8_{233B80DE-8EB8-4703-81E6-E4BFAD30342A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FA78556-1706-42A6-8ADF-3C051CAA064B}"/>
+  <xr:revisionPtr revIDLastSave="231" documentId="8_{233B80DE-8EB8-4703-81E6-E4BFAD30342A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1D3347C-A91A-440F-B618-577A4243D235}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{9B6553C3-9459-44AD-8511-B7B881CED92D}"/>
   </bookViews>
@@ -36,13 +36,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>USERID</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김태성</t>
   </si>
   <si>
     <t>time_start</t>
@@ -61,7 +58,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>홍길동</t>
+    <t>discord_UID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -201,10 +198,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -524,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F03C1A5-848F-412E-B7A8-07F492083FE9}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.75" style="1" customWidth="1"/>
@@ -532,46 +525,28 @@
     <col min="3" max="3" width="21.25" style="3" customWidth="1"/>
     <col min="4" max="4" width="16.75" style="3" customWidth="1"/>
     <col min="5" max="5" width="25.875" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="18.375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3">
-        <v>1725531325.437336</v>
-      </c>
-      <c r="C3" s="3">
-        <v>1725531552.1440618</v>
-      </c>
-      <c r="D3" s="3">
-        <v>226.70672583580017</v>
-      </c>
-      <c r="E3" s="2">
-        <v>226.70672583580017</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
